--- a/_ConfigExcels/Datas/recipe.xlsx
+++ b/_ConfigExcels/Datas/recipe.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,6 +433,9 @@
       <c r="K1" t="str">
         <v>unlock_day</v>
       </c>
+      <c r="L1" t="str">
+        <v>icon</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -468,6 +471,9 @@
       <c r="K2" t="str">
         <v>int</v>
       </c>
+      <c r="L2" t="str">
+        <v>string</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -503,6 +509,9 @@
       <c r="K3" t="str">
         <v>解锁天数</v>
       </c>
+      <c r="L3" t="str">
+        <v>图标资源路径</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -538,6 +547,9 @@
       <c r="K4">
         <v>1</v>
       </c>
+      <c r="L4" t="str">
+        <v>product_crystal</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -573,6 +585,9 @@
       <c r="K5">
         <v>1</v>
       </c>
+      <c r="L5" t="str">
+        <v>product_potion</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -608,6 +623,9 @@
       <c r="K6">
         <v>3</v>
       </c>
+      <c r="L6" t="str">
+        <v>product_potion</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -643,6 +661,9 @@
       <c r="K7">
         <v>5</v>
       </c>
+      <c r="L7" t="str">
+        <v>product_crystal</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -678,6 +699,9 @@
       <c r="K8">
         <v>8</v>
       </c>
+      <c r="L8" t="str">
+        <v>product_crystal</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -713,6 +737,9 @@
       <c r="K9">
         <v>10</v>
       </c>
+      <c r="L9" t="str">
+        <v>product_potion</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -748,6 +775,9 @@
       <c r="K10">
         <v>2</v>
       </c>
+      <c r="L10" t="str">
+        <v>product_potion</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -783,10 +813,13 @@
       <c r="K11">
         <v>2</v>
       </c>
+      <c r="L11" t="str">
+        <v>product_crystal</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>